--- a/data/employees/EMP024/AST-EMP024-06.xlsx
+++ b/data/employees/EMP024/AST-EMP024-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Resource Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,210 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Project Resource Tracker - Morgan Smith (Engineering)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Morgan Smith | Role: Engineer | Location: Fremont | Date: 2025-02-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>74</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Resources</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>80</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Proj Alpha</t>
+          <t>EMP024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M1 - Design</t>
+          <t>Ast Emp024 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Team A</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2025-01-29</t>
-        </is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>95</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
+          <t>Section 1: Automation backlog refinement. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Proj Beta</t>
+          <t>EMP024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M2 - Build</t>
+          <t>Ast Emp024 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Team B</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>95</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Delayed</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
+          <t>Section 1: Department KPI performance. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Proj Gamma</t>
+          <t>EMP024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M1 - Design</t>
+          <t>Ast Emp024 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Team C</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>60</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
+          <t>Section 1: Knowledge transfer and onboarding. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Proj Delta</t>
+          <t>EMP024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M3 - Test</t>
+          <t>Ast Emp024 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Team A</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
-        </is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>75</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>At Risk</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
+          <t>Section 1: Data quality remediation. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>82</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>83</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>88</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>67</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>95</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>67</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>75</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>76</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>86</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>89</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>77</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>89</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>83</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>62</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>84</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>71</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp024 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>95</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP024</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP024 contributes to ast emp024 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>